--- a/bus-service-management-system/src/main/resources/excel/lineRoutesList.xlsx
+++ b/bus-service-management-system/src/main/resources/excel/lineRoutesList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\bus-service-management-system\src\main\resources\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\busServiceManagement\src\main\resources\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E209C4B9-C781-4702-8276-13F5957A33D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20CB152-29E4-4E1E-8E4D-7F033EEA848C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="24" windowWidth="18228" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29220" yWindow="1875" windowWidth="21600" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="系統一覧出力" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>系統ID</t>
   </si>
@@ -109,6 +109,13 @@
     <t>系統停留所ID</t>
     <rPh sb="0" eb="2">
       <t>ケイトウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>路線停留所ID</t>
+    <rPh sb="0" eb="5">
+      <t>ロセンテイリュウジョ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -544,14 +551,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V1"/>
-  <sheetFormatPr defaultColWidth="1.6640625" defaultRowHeight="18"/>
+  <dimension ref="A1:W1"/>
+  <sheetFormatPr defaultColWidth="1.7109375" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="22" width="20.6640625" style="2" customWidth="1"/>
-    <col min="23" max="16384" width="1.6640625" style="2"/>
+    <col min="1" max="23" width="20.7109375" style="2" customWidth="1"/>
+    <col min="24" max="16384" width="1.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -592,30 +599,33 @@
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
